--- a/ResultsFromPublication/ResultFiles/PlasmidSankey.xlsx
+++ b/ResultsFromPublication/ResultFiles/PlasmidSankey.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10726"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10821"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/cccon/Documents/GitHub/PlasmidToolBenchMarking/ResultsFromPublication/ResultFiles/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAD0439E-5303-2B40-A8AF-3289FDB82CCE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{16F31786-7009-FF45-9C79-08C0E5B30801}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="11900" yWindow="2160" windowWidth="30240" windowHeight="23140" xr2:uid="{C255343D-B30C-2240-975B-FA4D46CAE60D}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="328" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="347" uniqueCount="90">
   <si>
     <t>Tools</t>
   </si>
@@ -251,9 +251,6 @@
     <t>Command Line Availability</t>
   </si>
   <si>
-    <t>Installation with Conda</t>
-  </si>
-  <si>
     <t>Successful Install</t>
   </si>
   <si>
@@ -300,6 +297,15 @@
   </si>
   <si>
     <t>Reads or Contigs</t>
+  </si>
+  <si>
+    <t>geNomad</t>
+  </si>
+  <si>
+    <t>PlasX</t>
+  </si>
+  <si>
+    <t>Installation</t>
   </si>
 </sst>
 </file>
@@ -693,7 +699,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5B04100A-B44B-EE48-8CA7-BBFF0160ECFA}">
-  <dimension ref="A1:K43"/>
+  <dimension ref="A1:K45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="36.5" bestFit="1" customWidth="1"/>
@@ -735,7 +741,7 @@
         <v>70</v>
       </c>
       <c r="I1" t="s">
-        <v>71</v>
+        <v>89</v>
       </c>
       <c r="J1" t="s">
         <v>68</v>
@@ -770,7 +776,7 @@
         <v>52</v>
       </c>
       <c r="I2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J2" s="4" t="s">
         <v>53</v>
@@ -829,7 +835,7 @@
         <v>52</v>
       </c>
       <c r="I4" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J4" s="4" t="s">
         <v>53</v>
@@ -864,7 +870,7 @@
         <v>52</v>
       </c>
       <c r="I5" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J5" s="4" t="s">
         <v>56</v>
@@ -896,7 +902,7 @@
         <v>52</v>
       </c>
       <c r="I6" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J6" s="4" t="s">
         <v>53</v>
@@ -931,7 +937,7 @@
         <v>52</v>
       </c>
       <c r="I7" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J7" s="4" t="s">
         <v>56</v>
@@ -987,7 +993,7 @@
         <v>52</v>
       </c>
       <c r="I9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J9" s="4" t="s">
         <v>56</v>
@@ -1070,7 +1076,7 @@
         <v>52</v>
       </c>
       <c r="I12" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J12" s="4" t="s">
         <v>56</v>
@@ -1084,7 +1090,7 @@
         <v>2018</v>
       </c>
       <c r="C13" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D13" t="s">
         <v>54</v>
@@ -1102,7 +1108,7 @@
         <v>52</v>
       </c>
       <c r="I13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J13" s="4" t="s">
         <v>53</v>
@@ -1137,7 +1143,7 @@
         <v>52</v>
       </c>
       <c r="I14" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J14" s="4" t="s">
         <v>56</v>
@@ -1169,7 +1175,7 @@
         <v>52</v>
       </c>
       <c r="I15" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J15" s="4"/>
     </row>
@@ -1199,7 +1205,7 @@
         <v>52</v>
       </c>
       <c r="I16" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J16" s="4" t="s">
         <v>56</v>
@@ -1252,7 +1258,7 @@
         <v>52</v>
       </c>
       <c r="I18" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J18" s="4" t="s">
         <v>53</v>
@@ -1335,7 +1341,7 @@
         <v>52</v>
       </c>
       <c r="I21" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="J21" s="4"/>
     </row>
@@ -1377,7 +1383,7 @@
         <v>54</v>
       </c>
       <c r="E23" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J23" s="4"/>
     </row>
@@ -1395,7 +1401,7 @@
         <v>54</v>
       </c>
       <c r="E24" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="J24" s="4"/>
     </row>
@@ -1488,7 +1494,7 @@
         <v>52</v>
       </c>
       <c r="I28" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J28" s="4" t="s">
         <v>53</v>
@@ -1523,7 +1529,7 @@
         <v>52</v>
       </c>
       <c r="I29" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J29" s="4" t="s">
         <v>56</v>
@@ -1555,7 +1561,7 @@
         <v>52</v>
       </c>
       <c r="I30" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="J30" s="4"/>
     </row>
@@ -1603,7 +1609,7 @@
         <v>52</v>
       </c>
       <c r="I32" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J32" s="4" t="s">
         <v>53</v>
@@ -1689,7 +1695,7 @@
         <v>52</v>
       </c>
       <c r="I35" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="J35" s="4"/>
     </row>
@@ -1719,7 +1725,7 @@
         <v>52</v>
       </c>
       <c r="I36" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J36" s="4" t="s">
         <v>53</v>
@@ -1730,7 +1736,7 @@
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A37" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B37">
         <v>2024</v>
@@ -1756,7 +1762,7 @@
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A38" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="B38">
         <v>2025</v>
@@ -1780,15 +1786,15 @@
         <v>52</v>
       </c>
       <c r="I38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J38" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="B39">
         <v>2025</v>
@@ -1814,13 +1820,13 @@
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A40" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B40">
         <v>2023</v>
       </c>
       <c r="C40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D40" t="s">
         <v>54</v>
@@ -1838,12 +1844,12 @@
         <v>52</v>
       </c>
       <c r="I40" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A41" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="B41">
         <v>2023</v>
@@ -1867,7 +1873,7 @@
         <v>52</v>
       </c>
       <c r="I41" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="J41" t="s">
         <v>56</v>
@@ -1875,13 +1881,13 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="B42">
         <v>2023</v>
       </c>
       <c r="C42" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="D42" t="s">
         <v>54</v>
@@ -1899,12 +1905,12 @@
         <v>52</v>
       </c>
       <c r="I42" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.2">
       <c r="A43" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B43">
         <v>2023</v>
@@ -1923,6 +1929,73 @@
       </c>
       <c r="G43" t="s">
         <v>57</v>
+      </c>
+    </row>
+    <row r="44" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>87</v>
+      </c>
+      <c r="B44">
+        <v>2023</v>
+      </c>
+      <c r="C44" t="s">
+        <v>41</v>
+      </c>
+      <c r="D44" t="s">
+        <v>54</v>
+      </c>
+      <c r="E44" t="s">
+        <v>61</v>
+      </c>
+      <c r="F44" t="s">
+        <v>62</v>
+      </c>
+      <c r="G44" t="s">
+        <v>55</v>
+      </c>
+      <c r="H44" t="s">
+        <v>52</v>
+      </c>
+      <c r="I44" t="s">
+        <v>71</v>
+      </c>
+      <c r="J44" t="s">
+        <v>53</v>
+      </c>
+      <c r="K44" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="45" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>88</v>
+      </c>
+      <c r="B45">
+        <v>2020</v>
+      </c>
+      <c r="C45" t="s">
+        <v>41</v>
+      </c>
+      <c r="D45" t="s">
+        <v>54</v>
+      </c>
+      <c r="E45" t="s">
+        <v>61</v>
+      </c>
+      <c r="F45" t="s">
+        <v>62</v>
+      </c>
+      <c r="G45" t="s">
+        <v>55</v>
+      </c>
+      <c r="H45" t="s">
+        <v>52</v>
+      </c>
+      <c r="I45" t="s">
+        <v>71</v>
+      </c>
+      <c r="J45" t="s">
+        <v>56</v>
       </c>
     </row>
   </sheetData>
